--- a/Exported_File.xlsx
+++ b/Exported_File.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2958C5A7-C73E-4015-8D24-0A48FEA7DD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9206516D-8D63-4364-835E-08D90FF24EAA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-10215" windowWidth="16440" windowHeight="29040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16320" yWindow="-10212" windowWidth="16440" windowHeight="29040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="قائمة التقييم" sheetId="2" r:id="rId1"/>
@@ -21,15 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -38,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="113">
   <si>
     <t>عناصــــــر التقييـــــم</t>
   </si>
@@ -116,9 +107,6 @@
   </si>
   <si>
     <t>أدخل اسم قائد الوحدة الخاضعة للتقييم</t>
-  </si>
-  <si>
-    <t>أدخل العلامة</t>
   </si>
   <si>
     <r>
@@ -1405,6 +1393,165 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="3" readingOrder="2"/>
     </xf>
@@ -1422,165 +1569,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="3" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2060,71 +2048,71 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J97"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="28.140625" style="1" customWidth="1"/>
-    <col min="5" max="7" width="9.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.109375" style="1" customWidth="1"/>
+    <col min="5" max="7" width="9.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.44140625" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="53" t="s">
-        <v>113</v>
-      </c>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-    </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+    </row>
+    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="59" t="s">
+      <c r="C2" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="59"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-    </row>
-    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+    </row>
+    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="59" t="s">
+      <c r="C3" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="59"/>
+      <c r="D3" s="50"/>
       <c r="E3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-    </row>
-    <row r="4" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+    </row>
+    <row r="4" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="5"/>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
@@ -2135,29 +2123,29 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="64" t="s">
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64" t="s">
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="65"/>
-    </row>
-    <row r="6" spans="1:10" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J5" s="56"/>
+    </row>
+    <row r="6" spans="1:10" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9"/>
-      <c r="B6" s="57"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
       <c r="E6" s="10" t="s">
         <v>3</v>
       </c>
@@ -2170,16 +2158,16 @@
       <c r="H6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="67"/>
-    </row>
-    <row r="7" spans="1:10" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I6" s="57"/>
+      <c r="J6" s="58"/>
+    </row>
+    <row r="7" spans="1:10" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9"/>
-      <c r="B7" s="62" t="s">
+      <c r="B7" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
       <c r="E7" s="11" t="s">
         <v>10</v>
       </c>
@@ -2192,1978 +2180,1593 @@
       <c r="H7" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="68" t="s">
+      <c r="I7" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="69"/>
-    </row>
-    <row r="8" spans="1:10" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J7" s="59"/>
+    </row>
+    <row r="8" spans="1:10" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9"/>
-      <c r="B8" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="36"/>
+      <c r="B8" s="65" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="66"/>
+      <c r="D8" s="67"/>
       <c r="E8" s="8">
         <v>10</v>
       </c>
-      <c r="F8" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="15" t="str">
-        <f>IFERROR(F8/E8,"")</f>
-        <v/>
-      </c>
+      <c r="F8" s="14"/>
+      <c r="G8" s="15"/>
       <c r="H8" s="13" t="str">
         <f>_xlfn.IFS(F8="أدخل العلامة","",F8="لا ينطبق","تم الإلغاء",G8&gt;=90%,"ممتاز",G8&gt;=80%,"جيد جداً",G8&gt;=70%,"جيد",G8&gt;=60%,"مقبول",G8&lt;60%,"راسب")</f>
-        <v/>
-      </c>
-      <c r="I8" s="42"/>
-      <c r="J8" s="43"/>
-    </row>
-    <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>راسب</v>
+      </c>
+      <c r="I8" s="28"/>
+      <c r="J8" s="29"/>
+    </row>
+    <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
-      <c r="B9" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="39"/>
+      <c r="B9" s="68" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="69"/>
+      <c r="D9" s="70"/>
       <c r="E9" s="16"/>
       <c r="F9" s="17"/>
       <c r="G9" s="18"/>
       <c r="H9" s="19"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="45"/>
-    </row>
-    <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I9" s="36"/>
+      <c r="J9" s="37"/>
+    </row>
+    <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="71" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="72"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="20">
+        <v>5</v>
+      </c>
+      <c r="F10" s="21"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="23" t="str">
+        <f t="shared" ref="H10:H73" si="0">_xlfn.IFS(F10="أدخل العلامة","",F10="لا ينطبق","تم الإلغاء",G10&gt;=90%,"ممتاز",G10&gt;=80%,"جيد جداً",G10&gt;=70%,"جيد",G10&gt;=60%,"مقبول",G10&lt;60%,"راسب")</f>
+        <v>راسب</v>
+      </c>
+      <c r="I10" s="32"/>
+      <c r="J10" s="33"/>
+    </row>
+    <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="20">
-        <v>5</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="22" t="str">
-        <f t="shared" ref="G10:G73" si="0">IFERROR(F10/E10,"")</f>
-        <v/>
-      </c>
-      <c r="H10" s="23" t="str">
-        <f t="shared" ref="H10:H73" si="1">_xlfn.IFS(F10="أدخل العلامة","",F10="لا ينطبق","تم الإلغاء",G10&gt;=90%,"ممتاز",G10&gt;=80%,"جيد جداً",G10&gt;=70%,"جيد",G10&gt;=60%,"مقبول",G10&lt;60%,"راسب")</f>
-        <v/>
-      </c>
-      <c r="I10" s="40"/>
-      <c r="J10" s="41"/>
-    </row>
-    <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
-      <c r="B11" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="30"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="73"/>
       <c r="E11" s="20">
         <v>8</v>
       </c>
-      <c r="F11" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F11" s="21"/>
+      <c r="G11" s="22"/>
       <c r="H11" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I11" s="40"/>
-      <c r="J11" s="41"/>
-    </row>
-    <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I11" s="32"/>
+      <c r="J11" s="33"/>
+    </row>
+    <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
-      <c r="B12" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="30"/>
+      <c r="B12" s="71" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="72"/>
+      <c r="D12" s="73"/>
       <c r="E12" s="20">
         <v>10</v>
       </c>
-      <c r="F12" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F12" s="21"/>
+      <c r="G12" s="22"/>
       <c r="H12" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I12" s="40"/>
-      <c r="J12" s="41"/>
-    </row>
-    <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I12" s="32"/>
+      <c r="J12" s="33"/>
+    </row>
+    <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="71" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="72"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="20">
+        <v>5</v>
+      </c>
+      <c r="F13" s="21"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I13" s="32"/>
+      <c r="J13" s="33"/>
+    </row>
+    <row r="14" spans="1:10" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="20">
-        <v>5</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H13" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I13" s="40"/>
-      <c r="J13" s="41"/>
-    </row>
-    <row r="14" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="30"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="73"/>
       <c r="E14" s="20">
         <v>10</v>
       </c>
-      <c r="F14" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F14" s="21"/>
+      <c r="G14" s="22"/>
       <c r="H14" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I14" s="40"/>
-      <c r="J14" s="41"/>
-    </row>
-    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I14" s="32"/>
+      <c r="J14" s="33"/>
+    </row>
+    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="71" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="72"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="20">
+        <v>5</v>
+      </c>
+      <c r="F15" s="21"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I15" s="32"/>
+      <c r="J15" s="33"/>
+    </row>
+    <row r="16" spans="1:10" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="9"/>
+      <c r="B16" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="20">
-        <v>5</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H15" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I15" s="40"/>
-      <c r="J15" s="41"/>
-    </row>
-    <row r="16" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="28" t="s">
+      <c r="C16" s="72"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="20">
+        <v>5</v>
+      </c>
+      <c r="F16" s="21"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I16" s="32"/>
+      <c r="J16" s="33"/>
+    </row>
+    <row r="17" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="9"/>
+      <c r="B17" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="20">
-        <v>5</v>
-      </c>
-      <c r="F16" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H16" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I16" s="40"/>
-      <c r="J16" s="41"/>
-    </row>
-    <row r="17" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="28" t="s">
+      <c r="C17" s="72"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="20">
+        <v>5</v>
+      </c>
+      <c r="F17" s="21"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I17" s="32"/>
+      <c r="J17" s="33"/>
+    </row>
+    <row r="18" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="9"/>
+      <c r="B18" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="29"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="20">
-        <v>5</v>
-      </c>
-      <c r="F17" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H17" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I17" s="40"/>
-      <c r="J17" s="41"/>
-    </row>
-    <row r="18" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="30"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="73"/>
       <c r="E18" s="20">
         <v>6</v>
       </c>
-      <c r="F18" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F18" s="21"/>
+      <c r="G18" s="22"/>
       <c r="H18" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I18" s="40"/>
-      <c r="J18" s="41"/>
-    </row>
-    <row r="19" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I18" s="32"/>
+      <c r="J18" s="33"/>
+    </row>
+    <row r="19" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
-      <c r="B19" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="30"/>
+      <c r="B19" s="71" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="72"/>
+      <c r="D19" s="73"/>
       <c r="E19" s="20">
         <v>8</v>
       </c>
-      <c r="F19" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F19" s="21"/>
+      <c r="G19" s="22"/>
       <c r="H19" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I19" s="40"/>
-      <c r="J19" s="41"/>
-    </row>
-    <row r="20" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I19" s="32"/>
+      <c r="J19" s="33"/>
+    </row>
+    <row r="20" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
-      <c r="B20" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="30"/>
+      <c r="B20" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="72"/>
+      <c r="D20" s="73"/>
       <c r="E20" s="20">
         <v>6</v>
       </c>
-      <c r="F20" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F20" s="21"/>
+      <c r="G20" s="22"/>
       <c r="H20" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I20" s="40"/>
-      <c r="J20" s="41"/>
-    </row>
-    <row r="21" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I20" s="32"/>
+      <c r="J20" s="33"/>
+    </row>
+    <row r="21" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9"/>
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="75"/>
+      <c r="D21" s="76"/>
+      <c r="E21" s="24">
+        <v>5</v>
+      </c>
+      <c r="F21" s="25"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I21" s="34"/>
+      <c r="J21" s="35"/>
+    </row>
+    <row r="22" spans="1:10" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="9"/>
+      <c r="B22" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="32"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="24">
-        <v>5</v>
-      </c>
-      <c r="F21" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H21" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I21" s="51"/>
-      <c r="J21" s="52"/>
-    </row>
-    <row r="22" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9"/>
-      <c r="B22" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="38"/>
-      <c r="D22" s="39"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="70"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="18"/>
       <c r="H22" s="19"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="45"/>
-    </row>
-    <row r="23" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I22" s="36"/>
+      <c r="J22" s="37"/>
+    </row>
+    <row r="23" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="71" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="72"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="20">
+        <v>5</v>
+      </c>
+      <c r="F23" s="21"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I23" s="32"/>
+      <c r="J23" s="33"/>
+    </row>
+    <row r="24" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="9"/>
+      <c r="B24" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="20">
-        <v>5</v>
-      </c>
-      <c r="F23" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H23" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I23" s="40"/>
-      <c r="J23" s="41"/>
-    </row>
-    <row r="24" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="9"/>
-      <c r="B24" s="28" t="s">
+      <c r="C24" s="72"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="20">
+        <v>5</v>
+      </c>
+      <c r="F24" s="21"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I24" s="32"/>
+      <c r="J24" s="33"/>
+    </row>
+    <row r="25" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="9"/>
+      <c r="B25" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="20">
-        <v>5</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H24" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I24" s="40"/>
-      <c r="J24" s="41"/>
-    </row>
-    <row r="25" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="9"/>
-      <c r="B25" s="28" t="s">
+      <c r="C25" s="72"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="20">
+        <v>5</v>
+      </c>
+      <c r="F25" s="21"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I25" s="32"/>
+      <c r="J25" s="33"/>
+    </row>
+    <row r="26" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="9"/>
+      <c r="B26" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="C25" s="29"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="20">
-        <v>5</v>
-      </c>
-      <c r="F25" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H25" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I25" s="40"/>
-      <c r="J25" s="41"/>
-    </row>
-    <row r="26" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="9"/>
-      <c r="B26" s="28" t="s">
+      <c r="C26" s="72"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="20">
+        <v>5</v>
+      </c>
+      <c r="F26" s="21"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I26" s="32"/>
+      <c r="J26" s="33"/>
+    </row>
+    <row r="27" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="9"/>
+      <c r="B27" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="20">
-        <v>5</v>
-      </c>
-      <c r="F26" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H26" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I26" s="40"/>
-      <c r="J26" s="41"/>
-    </row>
-    <row r="27" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="9"/>
-      <c r="B27" s="28" t="s">
+      <c r="C27" s="72"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="20">
+        <v>5</v>
+      </c>
+      <c r="F27" s="21"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I27" s="32"/>
+      <c r="J27" s="33"/>
+    </row>
+    <row r="28" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="9"/>
+      <c r="B28" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="29"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="20">
-        <v>5</v>
-      </c>
-      <c r="F27" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H27" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I27" s="40"/>
-      <c r="J27" s="41"/>
-    </row>
-    <row r="28" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="9"/>
-      <c r="B28" s="28" t="s">
+      <c r="C28" s="72"/>
+      <c r="D28" s="73"/>
+      <c r="E28" s="20">
+        <v>5</v>
+      </c>
+      <c r="F28" s="21"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I28" s="32"/>
+      <c r="J28" s="33"/>
+    </row>
+    <row r="29" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="9"/>
+      <c r="B29" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="20">
-        <v>5</v>
-      </c>
-      <c r="F28" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G28" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H28" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I28" s="40"/>
-      <c r="J28" s="41"/>
-    </row>
-    <row r="29" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="31" t="s">
+      <c r="C29" s="75"/>
+      <c r="D29" s="76"/>
+      <c r="E29" s="24">
+        <v>5</v>
+      </c>
+      <c r="F29" s="25"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I29" s="34"/>
+      <c r="J29" s="35"/>
+    </row>
+    <row r="30" spans="1:10" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="9"/>
+      <c r="B30" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="32"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="24">
-        <v>5</v>
-      </c>
-      <c r="F29" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H29" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I29" s="51"/>
-      <c r="J29" s="52"/>
-    </row>
-    <row r="30" spans="1:10" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="9"/>
-      <c r="B30" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="C30" s="35"/>
-      <c r="D30" s="36"/>
+      <c r="C30" s="66"/>
+      <c r="D30" s="67"/>
       <c r="E30" s="8">
         <v>6</v>
       </c>
-      <c r="F30" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F30" s="14"/>
+      <c r="G30" s="15"/>
       <c r="H30" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I30" s="42"/>
-      <c r="J30" s="43"/>
-    </row>
-    <row r="31" spans="1:10" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I30" s="28"/>
+      <c r="J30" s="29"/>
+    </row>
+    <row r="31" spans="1:10" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9"/>
-      <c r="B31" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" s="35"/>
-      <c r="D31" s="36"/>
+      <c r="B31" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" s="66"/>
+      <c r="D31" s="67"/>
       <c r="E31" s="8">
         <v>6</v>
       </c>
-      <c r="F31" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F31" s="14"/>
+      <c r="G31" s="15"/>
       <c r="H31" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I31" s="42"/>
-      <c r="J31" s="43"/>
-    </row>
-    <row r="32" spans="1:10" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I31" s="28"/>
+      <c r="J31" s="29"/>
+    </row>
+    <row r="32" spans="1:10" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="9"/>
-      <c r="B32" s="34" t="s">
+      <c r="B32" s="65" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="66"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="8">
+        <v>5</v>
+      </c>
+      <c r="F32" s="14"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I32" s="28"/>
+      <c r="J32" s="29"/>
+    </row>
+    <row r="33" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="9"/>
+      <c r="B33" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="C32" s="35"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="8">
-        <v>5</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H32" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I32" s="42"/>
-      <c r="J32" s="43"/>
-    </row>
-    <row r="33" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="9"/>
-      <c r="B33" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" s="38"/>
-      <c r="D33" s="39"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="70"/>
       <c r="E33" s="16"/>
       <c r="F33" s="17"/>
       <c r="G33" s="18"/>
       <c r="H33" s="19"/>
-      <c r="I33" s="44"/>
-      <c r="J33" s="45"/>
-    </row>
-    <row r="34" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I33" s="36"/>
+      <c r="J33" s="37"/>
+    </row>
+    <row r="34" spans="1:10" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
-      <c r="B34" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C34" s="29"/>
-      <c r="D34" s="30"/>
+      <c r="B34" s="71" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="72"/>
+      <c r="D34" s="73"/>
       <c r="E34" s="20">
         <v>6</v>
       </c>
-      <c r="F34" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F34" s="21"/>
+      <c r="G34" s="22"/>
       <c r="H34" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I34" s="40"/>
-      <c r="J34" s="41"/>
-    </row>
-    <row r="35" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I34" s="32"/>
+      <c r="J34" s="33"/>
+    </row>
+    <row r="35" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9"/>
-      <c r="B35" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="30"/>
+      <c r="B35" s="71" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="72"/>
+      <c r="D35" s="73"/>
       <c r="E35" s="20">
         <v>6</v>
       </c>
-      <c r="F35" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F35" s="21"/>
+      <c r="G35" s="22"/>
       <c r="H35" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I35" s="40"/>
-      <c r="J35" s="41"/>
-    </row>
-    <row r="36" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I35" s="32"/>
+      <c r="J35" s="33"/>
+    </row>
+    <row r="36" spans="1:10" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9"/>
-      <c r="B36" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" s="29"/>
-      <c r="D36" s="30"/>
+      <c r="B36" s="71" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="72"/>
+      <c r="D36" s="73"/>
       <c r="E36" s="20">
         <v>6</v>
       </c>
-      <c r="F36" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F36" s="21"/>
+      <c r="G36" s="22"/>
       <c r="H36" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I36" s="40"/>
-      <c r="J36" s="41"/>
-    </row>
-    <row r="37" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I36" s="32"/>
+      <c r="J36" s="33"/>
+    </row>
+    <row r="37" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9"/>
-      <c r="B37" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="C37" s="29"/>
-      <c r="D37" s="30"/>
+      <c r="B37" s="71" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="72"/>
+      <c r="D37" s="73"/>
       <c r="E37" s="20">
         <v>6</v>
       </c>
-      <c r="F37" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F37" s="21"/>
+      <c r="G37" s="22"/>
       <c r="H37" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I37" s="40"/>
-      <c r="J37" s="41"/>
-    </row>
-    <row r="38" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I37" s="32"/>
+      <c r="J37" s="33"/>
+    </row>
+    <row r="38" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
-      <c r="B38" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="C38" s="29"/>
-      <c r="D38" s="30"/>
+      <c r="B38" s="71" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" s="72"/>
+      <c r="D38" s="73"/>
       <c r="E38" s="20">
         <v>6</v>
       </c>
-      <c r="F38" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F38" s="21"/>
+      <c r="G38" s="22"/>
       <c r="H38" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I38" s="40"/>
-      <c r="J38" s="41"/>
-    </row>
-    <row r="39" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I38" s="32"/>
+      <c r="J38" s="33"/>
+    </row>
+    <row r="39" spans="1:10" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="9"/>
-      <c r="B39" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C39" s="29"/>
-      <c r="D39" s="30"/>
+      <c r="B39" s="71" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" s="72"/>
+      <c r="D39" s="73"/>
       <c r="E39" s="20">
         <v>6</v>
       </c>
-      <c r="F39" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F39" s="21"/>
+      <c r="G39" s="22"/>
       <c r="H39" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I39" s="40"/>
-      <c r="J39" s="41"/>
-    </row>
-    <row r="40" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I39" s="32"/>
+      <c r="J39" s="33"/>
+    </row>
+    <row r="40" spans="1:10" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="9"/>
-      <c r="B40" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="C40" s="29"/>
-      <c r="D40" s="30"/>
+      <c r="B40" s="71" t="s">
+        <v>59</v>
+      </c>
+      <c r="C40" s="72"/>
+      <c r="D40" s="73"/>
       <c r="E40" s="20">
         <v>6</v>
       </c>
-      <c r="F40" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F40" s="21"/>
+      <c r="G40" s="22"/>
       <c r="H40" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I40" s="40"/>
-      <c r="J40" s="41"/>
-    </row>
-    <row r="41" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I40" s="32"/>
+      <c r="J40" s="33"/>
+    </row>
+    <row r="41" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="9"/>
-      <c r="B41" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="C41" s="29"/>
-      <c r="D41" s="30"/>
+      <c r="B41" s="71" t="s">
+        <v>60</v>
+      </c>
+      <c r="C41" s="72"/>
+      <c r="D41" s="73"/>
       <c r="E41" s="20">
         <v>6</v>
       </c>
-      <c r="F41" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F41" s="21"/>
+      <c r="G41" s="22"/>
       <c r="H41" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I41" s="40"/>
-      <c r="J41" s="41"/>
-    </row>
-    <row r="42" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I41" s="32"/>
+      <c r="J41" s="33"/>
+    </row>
+    <row r="42" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9"/>
-      <c r="B42" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="C42" s="29"/>
-      <c r="D42" s="30"/>
+      <c r="B42" s="71" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42" s="72"/>
+      <c r="D42" s="73"/>
       <c r="E42" s="20">
         <v>6</v>
       </c>
-      <c r="F42" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F42" s="21"/>
+      <c r="G42" s="22"/>
       <c r="H42" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I42" s="40"/>
-      <c r="J42" s="41"/>
-    </row>
-    <row r="43" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I42" s="32"/>
+      <c r="J42" s="33"/>
+    </row>
+    <row r="43" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9"/>
-      <c r="B43" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C43" s="29"/>
-      <c r="D43" s="30"/>
+      <c r="B43" s="71" t="s">
+        <v>62</v>
+      </c>
+      <c r="C43" s="72"/>
+      <c r="D43" s="73"/>
       <c r="E43" s="20">
         <v>6</v>
       </c>
-      <c r="F43" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F43" s="21"/>
+      <c r="G43" s="22"/>
       <c r="H43" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I43" s="40"/>
-      <c r="J43" s="41"/>
-    </row>
-    <row r="44" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I43" s="32"/>
+      <c r="J43" s="33"/>
+    </row>
+    <row r="44" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="9"/>
-      <c r="B44" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="C44" s="29"/>
-      <c r="D44" s="30"/>
+      <c r="B44" s="71" t="s">
+        <v>63</v>
+      </c>
+      <c r="C44" s="72"/>
+      <c r="D44" s="73"/>
       <c r="E44" s="20">
         <v>6</v>
       </c>
-      <c r="F44" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F44" s="21"/>
+      <c r="G44" s="22"/>
       <c r="H44" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I44" s="40"/>
-      <c r="J44" s="41"/>
-    </row>
-    <row r="45" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I44" s="32"/>
+      <c r="J44" s="33"/>
+    </row>
+    <row r="45" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="9"/>
-      <c r="B45" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="C45" s="29"/>
-      <c r="D45" s="30"/>
+      <c r="B45" s="71" t="s">
+        <v>64</v>
+      </c>
+      <c r="C45" s="72"/>
+      <c r="D45" s="73"/>
       <c r="E45" s="20">
         <v>6</v>
       </c>
-      <c r="F45" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F45" s="21"/>
+      <c r="G45" s="22"/>
       <c r="H45" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I45" s="40"/>
-      <c r="J45" s="41"/>
-    </row>
-    <row r="46" spans="1:10" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I45" s="32"/>
+      <c r="J45" s="33"/>
+    </row>
+    <row r="46" spans="1:10" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9"/>
-      <c r="B46" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="C46" s="32"/>
-      <c r="D46" s="33"/>
+      <c r="B46" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46" s="75"/>
+      <c r="D46" s="76"/>
       <c r="E46" s="24">
         <v>10</v>
       </c>
-      <c r="F46" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F46" s="25"/>
+      <c r="G46" s="26"/>
       <c r="H46" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I46" s="51"/>
-      <c r="J46" s="52"/>
-    </row>
-    <row r="47" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I46" s="34"/>
+      <c r="J46" s="35"/>
+    </row>
+    <row r="47" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9"/>
-      <c r="B47" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="C47" s="38"/>
-      <c r="D47" s="39"/>
+      <c r="B47" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="C47" s="69"/>
+      <c r="D47" s="70"/>
       <c r="E47" s="16"/>
       <c r="F47" s="17"/>
       <c r="G47" s="18"/>
       <c r="H47" s="19"/>
-      <c r="I47" s="44"/>
-      <c r="J47" s="45"/>
-    </row>
-    <row r="48" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I47" s="36"/>
+      <c r="J47" s="37"/>
+    </row>
+    <row r="48" spans="1:10" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9"/>
-      <c r="B48" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="C48" s="29"/>
-      <c r="D48" s="30"/>
+      <c r="B48" s="71" t="s">
+        <v>67</v>
+      </c>
+      <c r="C48" s="72"/>
+      <c r="D48" s="73"/>
       <c r="E48" s="20">
         <v>10</v>
       </c>
-      <c r="F48" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G48" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F48" s="21"/>
+      <c r="G48" s="22"/>
       <c r="H48" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I48" s="40"/>
-      <c r="J48" s="41"/>
-    </row>
-    <row r="49" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I48" s="32"/>
+      <c r="J48" s="33"/>
+    </row>
+    <row r="49" spans="1:10" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9"/>
-      <c r="B49" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="C49" s="29"/>
-      <c r="D49" s="30"/>
+      <c r="B49" s="71" t="s">
+        <v>68</v>
+      </c>
+      <c r="C49" s="72"/>
+      <c r="D49" s="73"/>
       <c r="E49" s="20">
         <v>10</v>
       </c>
-      <c r="F49" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F49" s="21"/>
+      <c r="G49" s="22"/>
       <c r="H49" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I49" s="40"/>
-      <c r="J49" s="41"/>
-    </row>
-    <row r="50" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I49" s="32"/>
+      <c r="J49" s="33"/>
+    </row>
+    <row r="50" spans="1:10" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="9"/>
-      <c r="B50" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" s="29"/>
-      <c r="D50" s="30"/>
+      <c r="B50" s="71" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50" s="72"/>
+      <c r="D50" s="73"/>
       <c r="E50" s="20">
         <v>8</v>
       </c>
-      <c r="F50" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F50" s="21"/>
+      <c r="G50" s="22"/>
       <c r="H50" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I50" s="40"/>
-      <c r="J50" s="41"/>
-    </row>
-    <row r="51" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I50" s="32"/>
+      <c r="J50" s="33"/>
+    </row>
+    <row r="51" spans="1:10" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="9"/>
-      <c r="B51" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C51" s="29"/>
-      <c r="D51" s="30"/>
+      <c r="B51" s="71" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" s="72"/>
+      <c r="D51" s="73"/>
       <c r="E51" s="20">
         <v>8</v>
       </c>
-      <c r="F51" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F51" s="21"/>
+      <c r="G51" s="22"/>
       <c r="H51" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I51" s="40"/>
-      <c r="J51" s="41"/>
-    </row>
-    <row r="52" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I51" s="32"/>
+      <c r="J51" s="33"/>
+    </row>
+    <row r="52" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="9"/>
-      <c r="B52" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="C52" s="29"/>
-      <c r="D52" s="30"/>
+      <c r="B52" s="71" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" s="72"/>
+      <c r="D52" s="73"/>
       <c r="E52" s="20">
         <v>8</v>
       </c>
-      <c r="F52" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F52" s="21"/>
+      <c r="G52" s="22"/>
       <c r="H52" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I52" s="40"/>
-      <c r="J52" s="41"/>
-    </row>
-    <row r="53" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I52" s="32"/>
+      <c r="J52" s="33"/>
+    </row>
+    <row r="53" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9"/>
-      <c r="B53" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="C53" s="32"/>
-      <c r="D53" s="33"/>
+      <c r="B53" s="74" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53" s="75"/>
+      <c r="D53" s="76"/>
       <c r="E53" s="24">
         <v>8</v>
       </c>
-      <c r="F53" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F53" s="25"/>
+      <c r="G53" s="26"/>
       <c r="H53" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I53" s="51"/>
-      <c r="J53" s="52"/>
-    </row>
-    <row r="54" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I53" s="34"/>
+      <c r="J53" s="35"/>
+    </row>
+    <row r="54" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="9"/>
-      <c r="B54" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="C54" s="38"/>
-      <c r="D54" s="39"/>
+      <c r="B54" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="C54" s="69"/>
+      <c r="D54" s="70"/>
       <c r="E54" s="16"/>
       <c r="F54" s="17"/>
       <c r="G54" s="18"/>
       <c r="H54" s="19"/>
-      <c r="I54" s="44"/>
-      <c r="J54" s="45"/>
-    </row>
-    <row r="55" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I54" s="36"/>
+      <c r="J54" s="37"/>
+    </row>
+    <row r="55" spans="1:10" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="9"/>
-      <c r="B55" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="C55" s="29"/>
-      <c r="D55" s="30"/>
+      <c r="B55" s="71" t="s">
+        <v>74</v>
+      </c>
+      <c r="C55" s="72"/>
+      <c r="D55" s="73"/>
       <c r="E55" s="20">
         <v>10</v>
       </c>
-      <c r="F55" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F55" s="21"/>
+      <c r="G55" s="22"/>
       <c r="H55" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I55" s="40"/>
-      <c r="J55" s="41"/>
-    </row>
-    <row r="56" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I55" s="32"/>
+      <c r="J55" s="33"/>
+    </row>
+    <row r="56" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="9"/>
-      <c r="B56" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C56" s="29"/>
-      <c r="D56" s="30"/>
+      <c r="B56" s="71" t="s">
+        <v>75</v>
+      </c>
+      <c r="C56" s="72"/>
+      <c r="D56" s="73"/>
       <c r="E56" s="20">
         <v>8</v>
       </c>
-      <c r="F56" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F56" s="21"/>
+      <c r="G56" s="22"/>
       <c r="H56" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I56" s="40"/>
-      <c r="J56" s="41"/>
-    </row>
-    <row r="57" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I56" s="32"/>
+      <c r="J56" s="33"/>
+    </row>
+    <row r="57" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="9"/>
-      <c r="B57" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="C57" s="29"/>
-      <c r="D57" s="30"/>
+      <c r="B57" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="C57" s="72"/>
+      <c r="D57" s="73"/>
       <c r="E57" s="20">
         <v>8</v>
       </c>
-      <c r="F57" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F57" s="21"/>
+      <c r="G57" s="22"/>
       <c r="H57" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I57" s="40"/>
-      <c r="J57" s="41"/>
-    </row>
-    <row r="58" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I57" s="32"/>
+      <c r="J57" s="33"/>
+    </row>
+    <row r="58" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="9"/>
-      <c r="B58" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="C58" s="32"/>
-      <c r="D58" s="33"/>
+      <c r="B58" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="C58" s="75"/>
+      <c r="D58" s="76"/>
       <c r="E58" s="24">
         <v>8</v>
       </c>
-      <c r="F58" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="G58" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F58" s="25"/>
+      <c r="G58" s="26"/>
       <c r="H58" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I58" s="51"/>
-      <c r="J58" s="52"/>
-    </row>
-    <row r="59" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I58" s="34"/>
+      <c r="J58" s="35"/>
+    </row>
+    <row r="59" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="9"/>
-      <c r="B59" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="C59" s="38"/>
-      <c r="D59" s="39"/>
+      <c r="B59" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="C59" s="69"/>
+      <c r="D59" s="70"/>
       <c r="E59" s="16"/>
       <c r="F59" s="17"/>
       <c r="G59" s="18"/>
       <c r="H59" s="19"/>
-      <c r="I59" s="44"/>
-      <c r="J59" s="45"/>
-    </row>
-    <row r="60" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I59" s="36"/>
+      <c r="J59" s="37"/>
+    </row>
+    <row r="60" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="9"/>
-      <c r="B60" s="28" t="s">
+      <c r="B60" s="71" t="s">
+        <v>79</v>
+      </c>
+      <c r="C60" s="72"/>
+      <c r="D60" s="73"/>
+      <c r="E60" s="20">
+        <v>5</v>
+      </c>
+      <c r="F60" s="21"/>
+      <c r="G60" s="22"/>
+      <c r="H60" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I60" s="32"/>
+      <c r="J60" s="33"/>
+    </row>
+    <row r="61" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="9"/>
+      <c r="B61" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="C60" s="29"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="20">
-        <v>5</v>
-      </c>
-      <c r="F60" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H60" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I60" s="40"/>
-      <c r="J60" s="41"/>
-    </row>
-    <row r="61" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="9"/>
-      <c r="B61" s="28" t="s">
+      <c r="C61" s="72"/>
+      <c r="D61" s="73"/>
+      <c r="E61" s="20">
+        <v>5</v>
+      </c>
+      <c r="F61" s="21"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I61" s="32"/>
+      <c r="J61" s="33"/>
+    </row>
+    <row r="62" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="9"/>
+      <c r="B62" s="71" t="s">
         <v>81</v>
       </c>
-      <c r="C61" s="29"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="20">
-        <v>5</v>
-      </c>
-      <c r="F61" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H61" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I61" s="40"/>
-      <c r="J61" s="41"/>
-    </row>
-    <row r="62" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="9"/>
-      <c r="B62" s="28" t="s">
+      <c r="C62" s="72"/>
+      <c r="D62" s="73"/>
+      <c r="E62" s="20">
+        <v>5</v>
+      </c>
+      <c r="F62" s="21"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I62" s="32"/>
+      <c r="J62" s="33"/>
+    </row>
+    <row r="63" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="9"/>
+      <c r="B63" s="71" t="s">
         <v>82</v>
       </c>
-      <c r="C62" s="29"/>
-      <c r="D62" s="30"/>
-      <c r="E62" s="20">
-        <v>5</v>
-      </c>
-      <c r="F62" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H62" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I62" s="40"/>
-      <c r="J62" s="41"/>
-    </row>
-    <row r="63" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="9"/>
-      <c r="B63" s="28" t="s">
+      <c r="C63" s="72"/>
+      <c r="D63" s="73"/>
+      <c r="E63" s="20">
+        <v>5</v>
+      </c>
+      <c r="F63" s="21"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I63" s="32"/>
+      <c r="J63" s="33"/>
+    </row>
+    <row r="64" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="9"/>
+      <c r="B64" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="C63" s="29"/>
-      <c r="D63" s="30"/>
-      <c r="E63" s="20">
-        <v>5</v>
-      </c>
-      <c r="F63" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H63" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I63" s="40"/>
-      <c r="J63" s="41"/>
-    </row>
-    <row r="64" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="9"/>
-      <c r="B64" s="28" t="s">
+      <c r="C64" s="72"/>
+      <c r="D64" s="73"/>
+      <c r="E64" s="20">
+        <v>5</v>
+      </c>
+      <c r="F64" s="21"/>
+      <c r="G64" s="22"/>
+      <c r="H64" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I64" s="32"/>
+      <c r="J64" s="33"/>
+    </row>
+    <row r="65" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="9"/>
+      <c r="B65" s="71" t="s">
         <v>84</v>
       </c>
-      <c r="C64" s="29"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="20">
-        <v>5</v>
-      </c>
-      <c r="F64" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H64" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I64" s="40"/>
-      <c r="J64" s="41"/>
-    </row>
-    <row r="65" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="9"/>
-      <c r="B65" s="28" t="s">
+      <c r="C65" s="72"/>
+      <c r="D65" s="73"/>
+      <c r="E65" s="20">
+        <v>5</v>
+      </c>
+      <c r="F65" s="21"/>
+      <c r="G65" s="22"/>
+      <c r="H65" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I65" s="32"/>
+      <c r="J65" s="33"/>
+    </row>
+    <row r="66" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="9"/>
+      <c r="B66" s="71" t="s">
         <v>85</v>
       </c>
-      <c r="C65" s="29"/>
-      <c r="D65" s="30"/>
-      <c r="E65" s="20">
-        <v>5</v>
-      </c>
-      <c r="F65" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G65" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H65" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I65" s="40"/>
-      <c r="J65" s="41"/>
-    </row>
-    <row r="66" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="9"/>
-      <c r="B66" s="28" t="s">
+      <c r="C66" s="72"/>
+      <c r="D66" s="73"/>
+      <c r="E66" s="20">
+        <v>5</v>
+      </c>
+      <c r="F66" s="21"/>
+      <c r="G66" s="22"/>
+      <c r="H66" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I66" s="32"/>
+      <c r="J66" s="33"/>
+    </row>
+    <row r="67" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="9"/>
+      <c r="B67" s="71" t="s">
         <v>86</v>
       </c>
-      <c r="C66" s="29"/>
-      <c r="D66" s="30"/>
-      <c r="E66" s="20">
-        <v>5</v>
-      </c>
-      <c r="F66" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G66" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H66" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I66" s="40"/>
-      <c r="J66" s="41"/>
-    </row>
-    <row r="67" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="9"/>
-      <c r="B67" s="28" t="s">
+      <c r="C67" s="72"/>
+      <c r="D67" s="73"/>
+      <c r="E67" s="20">
+        <v>5</v>
+      </c>
+      <c r="F67" s="21"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I67" s="32"/>
+      <c r="J67" s="33"/>
+    </row>
+    <row r="68" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="9"/>
+      <c r="B68" s="71" t="s">
         <v>87</v>
       </c>
-      <c r="C67" s="29"/>
-      <c r="D67" s="30"/>
-      <c r="E67" s="20">
-        <v>5</v>
-      </c>
-      <c r="F67" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G67" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H67" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I67" s="40"/>
-      <c r="J67" s="41"/>
-    </row>
-    <row r="68" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="9"/>
-      <c r="B68" s="28" t="s">
+      <c r="C68" s="72"/>
+      <c r="D68" s="73"/>
+      <c r="E68" s="20">
+        <v>5</v>
+      </c>
+      <c r="F68" s="21"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I68" s="32"/>
+      <c r="J68" s="33"/>
+    </row>
+    <row r="69" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="9"/>
+      <c r="B69" s="71" t="s">
         <v>88</v>
       </c>
-      <c r="C68" s="29"/>
-      <c r="D68" s="30"/>
-      <c r="E68" s="20">
-        <v>5</v>
-      </c>
-      <c r="F68" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G68" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H68" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I68" s="40"/>
-      <c r="J68" s="41"/>
-    </row>
-    <row r="69" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="9"/>
-      <c r="B69" s="28" t="s">
+      <c r="C69" s="72"/>
+      <c r="D69" s="73"/>
+      <c r="E69" s="20">
+        <v>5</v>
+      </c>
+      <c r="F69" s="21"/>
+      <c r="G69" s="22"/>
+      <c r="H69" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I69" s="32"/>
+      <c r="J69" s="33"/>
+    </row>
+    <row r="70" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="9"/>
+      <c r="B70" s="71" t="s">
         <v>89</v>
       </c>
-      <c r="C69" s="29"/>
-      <c r="D69" s="30"/>
-      <c r="E69" s="20">
-        <v>5</v>
-      </c>
-      <c r="F69" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G69" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H69" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I69" s="40"/>
-      <c r="J69" s="41"/>
-    </row>
-    <row r="70" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="9"/>
-      <c r="B70" s="28" t="s">
+      <c r="C70" s="72"/>
+      <c r="D70" s="73"/>
+      <c r="E70" s="20">
+        <v>5</v>
+      </c>
+      <c r="F70" s="21"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I70" s="32"/>
+      <c r="J70" s="33"/>
+    </row>
+    <row r="71" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="9"/>
+      <c r="B71" s="71" t="s">
         <v>90</v>
       </c>
-      <c r="C70" s="29"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="20">
-        <v>5</v>
-      </c>
-      <c r="F70" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G70" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H70" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I70" s="40"/>
-      <c r="J70" s="41"/>
-    </row>
-    <row r="71" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="9"/>
-      <c r="B71" s="28" t="s">
+      <c r="C71" s="72"/>
+      <c r="D71" s="73"/>
+      <c r="E71" s="20">
+        <v>5</v>
+      </c>
+      <c r="F71" s="21"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I71" s="32"/>
+      <c r="J71" s="33"/>
+    </row>
+    <row r="72" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="9"/>
+      <c r="B72" s="71" t="s">
         <v>91</v>
       </c>
-      <c r="C71" s="29"/>
-      <c r="D71" s="30"/>
-      <c r="E71" s="20">
-        <v>5</v>
-      </c>
-      <c r="F71" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H71" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I71" s="40"/>
-      <c r="J71" s="41"/>
-    </row>
-    <row r="72" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="9"/>
-      <c r="B72" s="28" t="s">
+      <c r="C72" s="72"/>
+      <c r="D72" s="73"/>
+      <c r="E72" s="20">
+        <v>5</v>
+      </c>
+      <c r="F72" s="21"/>
+      <c r="G72" s="22"/>
+      <c r="H72" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I72" s="32"/>
+      <c r="J72" s="33"/>
+    </row>
+    <row r="73" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="9"/>
+      <c r="B73" s="74" t="s">
         <v>92</v>
       </c>
-      <c r="C72" s="29"/>
-      <c r="D72" s="30"/>
-      <c r="E72" s="20">
-        <v>5</v>
-      </c>
-      <c r="F72" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G72" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H72" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I72" s="40"/>
-      <c r="J72" s="41"/>
-    </row>
-    <row r="73" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="9"/>
-      <c r="B73" s="31" t="s">
+      <c r="C73" s="75"/>
+      <c r="D73" s="76"/>
+      <c r="E73" s="24">
+        <v>5</v>
+      </c>
+      <c r="F73" s="25"/>
+      <c r="G73" s="26"/>
+      <c r="H73" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>راسب</v>
+      </c>
+      <c r="I73" s="34"/>
+      <c r="J73" s="35"/>
+    </row>
+    <row r="74" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="9"/>
+      <c r="B74" s="68" t="s">
         <v>93</v>
       </c>
-      <c r="C73" s="32"/>
-      <c r="D73" s="33"/>
-      <c r="E73" s="24">
-        <v>5</v>
-      </c>
-      <c r="F73" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H73" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I73" s="51"/>
-      <c r="J73" s="52"/>
-    </row>
-    <row r="74" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="9"/>
-      <c r="B74" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="C74" s="38"/>
-      <c r="D74" s="39"/>
+      <c r="C74" s="69"/>
+      <c r="D74" s="70"/>
       <c r="E74" s="16"/>
       <c r="F74" s="17"/>
       <c r="G74" s="18"/>
       <c r="H74" s="19"/>
-      <c r="I74" s="44"/>
-      <c r="J74" s="45"/>
-    </row>
-    <row r="75" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I74" s="36"/>
+      <c r="J74" s="37"/>
+    </row>
+    <row r="75" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="9"/>
-      <c r="B75" s="28" t="s">
+      <c r="B75" s="71" t="s">
+        <v>94</v>
+      </c>
+      <c r="C75" s="72"/>
+      <c r="D75" s="73"/>
+      <c r="E75" s="20">
+        <v>5</v>
+      </c>
+      <c r="F75" s="21"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="23" t="str">
+        <f t="shared" ref="H75:H92" si="1">_xlfn.IFS(F75="أدخل العلامة","",F75="لا ينطبق","تم الإلغاء",G75&gt;=90%,"ممتاز",G75&gt;=80%,"جيد جداً",G75&gt;=70%,"جيد",G75&gt;=60%,"مقبول",G75&lt;60%,"راسب")</f>
+        <v>راسب</v>
+      </c>
+      <c r="I75" s="32"/>
+      <c r="J75" s="33"/>
+    </row>
+    <row r="76" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="9"/>
+      <c r="B76" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="C75" s="29"/>
-      <c r="D75" s="30"/>
-      <c r="E75" s="20">
-        <v>5</v>
-      </c>
-      <c r="F75" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G75" s="22" t="str">
-        <f t="shared" ref="G75:G92" si="2">IFERROR(F75/E75,"")</f>
-        <v/>
-      </c>
-      <c r="H75" s="23" t="str">
-        <f t="shared" ref="H75:H92" si="3">_xlfn.IFS(F75="أدخل العلامة","",F75="لا ينطبق","تم الإلغاء",G75&gt;=90%,"ممتاز",G75&gt;=80%,"جيد جداً",G75&gt;=70%,"جيد",G75&gt;=60%,"مقبول",G75&lt;60%,"راسب")</f>
-        <v/>
-      </c>
-      <c r="I75" s="40"/>
-      <c r="J75" s="41"/>
-    </row>
-    <row r="76" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="9"/>
-      <c r="B76" s="28" t="s">
+      <c r="C76" s="72"/>
+      <c r="D76" s="73"/>
+      <c r="E76" s="20">
+        <v>5</v>
+      </c>
+      <c r="F76" s="21"/>
+      <c r="G76" s="22"/>
+      <c r="H76" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>راسب</v>
+      </c>
+      <c r="I76" s="32"/>
+      <c r="J76" s="33"/>
+    </row>
+    <row r="77" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="9"/>
+      <c r="B77" s="71" t="s">
         <v>96</v>
       </c>
-      <c r="C76" s="29"/>
-      <c r="D76" s="30"/>
-      <c r="E76" s="20">
-        <v>5</v>
-      </c>
-      <c r="F76" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G76" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="H76" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I76" s="40"/>
-      <c r="J76" s="41"/>
-    </row>
-    <row r="77" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="9"/>
-      <c r="B77" s="28" t="s">
+      <c r="C77" s="72"/>
+      <c r="D77" s="73"/>
+      <c r="E77" s="20">
+        <v>5</v>
+      </c>
+      <c r="F77" s="21"/>
+      <c r="G77" s="22"/>
+      <c r="H77" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>راسب</v>
+      </c>
+      <c r="I77" s="32"/>
+      <c r="J77" s="33"/>
+    </row>
+    <row r="78" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="9"/>
+      <c r="B78" s="71" t="s">
         <v>97</v>
       </c>
-      <c r="C77" s="29"/>
-      <c r="D77" s="30"/>
-      <c r="E77" s="20">
-        <v>5</v>
-      </c>
-      <c r="F77" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="H77" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I77" s="40"/>
-      <c r="J77" s="41"/>
-    </row>
-    <row r="78" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="9"/>
-      <c r="B78" s="28" t="s">
+      <c r="C78" s="72"/>
+      <c r="D78" s="73"/>
+      <c r="E78" s="20">
+        <v>5</v>
+      </c>
+      <c r="F78" s="21"/>
+      <c r="G78" s="22"/>
+      <c r="H78" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>راسب</v>
+      </c>
+      <c r="I78" s="32"/>
+      <c r="J78" s="33"/>
+    </row>
+    <row r="79" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="9"/>
+      <c r="B79" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="C78" s="29"/>
-      <c r="D78" s="30"/>
-      <c r="E78" s="20">
-        <v>5</v>
-      </c>
-      <c r="F78" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="H78" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I78" s="40"/>
-      <c r="J78" s="41"/>
-    </row>
-    <row r="79" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="9"/>
-      <c r="B79" s="28" t="s">
+      <c r="C79" s="72"/>
+      <c r="D79" s="73"/>
+      <c r="E79" s="20">
+        <v>5</v>
+      </c>
+      <c r="F79" s="21"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>راسب</v>
+      </c>
+      <c r="I79" s="32"/>
+      <c r="J79" s="33"/>
+    </row>
+    <row r="80" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="9"/>
+      <c r="B80" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="C79" s="29"/>
-      <c r="D79" s="30"/>
-      <c r="E79" s="20">
-        <v>5</v>
-      </c>
-      <c r="F79" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G79" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="H79" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I79" s="40"/>
-      <c r="J79" s="41"/>
-    </row>
-    <row r="80" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="9"/>
-      <c r="B80" s="28" t="s">
+      <c r="C80" s="72"/>
+      <c r="D80" s="73"/>
+      <c r="E80" s="20">
+        <v>5</v>
+      </c>
+      <c r="F80" s="21"/>
+      <c r="G80" s="22"/>
+      <c r="H80" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>راسب</v>
+      </c>
+      <c r="I80" s="32"/>
+      <c r="J80" s="33"/>
+    </row>
+    <row r="81" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="9"/>
+      <c r="B81" s="71" t="s">
         <v>100</v>
       </c>
-      <c r="C80" s="29"/>
-      <c r="D80" s="30"/>
-      <c r="E80" s="20">
-        <v>5</v>
-      </c>
-      <c r="F80" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G80" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="H80" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I80" s="40"/>
-      <c r="J80" s="41"/>
-    </row>
-    <row r="81" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="9"/>
-      <c r="B81" s="28" t="s">
+      <c r="C81" s="72"/>
+      <c r="D81" s="73"/>
+      <c r="E81" s="20">
+        <v>5</v>
+      </c>
+      <c r="F81" s="21"/>
+      <c r="G81" s="22"/>
+      <c r="H81" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>راسب</v>
+      </c>
+      <c r="I81" s="32"/>
+      <c r="J81" s="33"/>
+    </row>
+    <row r="82" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="9"/>
+      <c r="B82" s="71" t="s">
         <v>101</v>
       </c>
-      <c r="C81" s="29"/>
-      <c r="D81" s="30"/>
-      <c r="E81" s="20">
-        <v>5</v>
-      </c>
-      <c r="F81" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="H81" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I81" s="40"/>
-      <c r="J81" s="41"/>
-    </row>
-    <row r="82" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="9"/>
-      <c r="B82" s="28" t="s">
+      <c r="C82" s="72"/>
+      <c r="D82" s="73"/>
+      <c r="E82" s="20">
+        <v>5</v>
+      </c>
+      <c r="F82" s="21"/>
+      <c r="G82" s="22"/>
+      <c r="H82" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>راسب</v>
+      </c>
+      <c r="I82" s="32"/>
+      <c r="J82" s="33"/>
+    </row>
+    <row r="83" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="9"/>
+      <c r="B83" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="C82" s="29"/>
-      <c r="D82" s="30"/>
-      <c r="E82" s="20">
-        <v>5</v>
-      </c>
-      <c r="F82" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G82" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="H82" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I82" s="40"/>
-      <c r="J82" s="41"/>
-    </row>
-    <row r="83" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="9"/>
-      <c r="B83" s="28" t="s">
+      <c r="C83" s="72"/>
+      <c r="D83" s="73"/>
+      <c r="E83" s="20">
+        <v>5</v>
+      </c>
+      <c r="F83" s="21"/>
+      <c r="G83" s="22"/>
+      <c r="H83" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>راسب</v>
+      </c>
+      <c r="I83" s="32"/>
+      <c r="J83" s="33"/>
+    </row>
+    <row r="84" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="9"/>
+      <c r="B84" s="71" t="s">
         <v>103</v>
       </c>
-      <c r="C83" s="29"/>
-      <c r="D83" s="30"/>
-      <c r="E83" s="20">
-        <v>5</v>
-      </c>
-      <c r="F83" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G83" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="H83" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I83" s="40"/>
-      <c r="J83" s="41"/>
-    </row>
-    <row r="84" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="9"/>
-      <c r="B84" s="28" t="s">
+      <c r="C84" s="72"/>
+      <c r="D84" s="73"/>
+      <c r="E84" s="20">
+        <v>5</v>
+      </c>
+      <c r="F84" s="21"/>
+      <c r="G84" s="22"/>
+      <c r="H84" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>راسب</v>
+      </c>
+      <c r="I84" s="32"/>
+      <c r="J84" s="33"/>
+    </row>
+    <row r="85" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="9"/>
+      <c r="B85" s="74" t="s">
         <v>104</v>
       </c>
-      <c r="C84" s="29"/>
-      <c r="D84" s="30"/>
-      <c r="E84" s="20">
-        <v>5</v>
-      </c>
-      <c r="F84" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G84" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="H84" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I84" s="40"/>
-      <c r="J84" s="41"/>
-    </row>
-    <row r="85" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="9"/>
-      <c r="B85" s="31" t="s">
+      <c r="C85" s="75"/>
+      <c r="D85" s="76"/>
+      <c r="E85" s="24">
+        <v>5</v>
+      </c>
+      <c r="F85" s="25"/>
+      <c r="G85" s="26"/>
+      <c r="H85" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>راسب</v>
+      </c>
+      <c r="I85" s="34"/>
+      <c r="J85" s="35"/>
+    </row>
+    <row r="86" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="9"/>
+      <c r="B86" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="C85" s="32"/>
-      <c r="D85" s="33"/>
-      <c r="E85" s="24">
-        <v>5</v>
-      </c>
-      <c r="F85" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="G85" s="26" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="H85" s="27" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I85" s="51"/>
-      <c r="J85" s="52"/>
-    </row>
-    <row r="86" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="9"/>
-      <c r="B86" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="C86" s="38"/>
-      <c r="D86" s="39"/>
+      <c r="C86" s="69"/>
+      <c r="D86" s="70"/>
       <c r="E86" s="16"/>
       <c r="F86" s="17"/>
       <c r="G86" s="18"/>
       <c r="H86" s="19"/>
-      <c r="I86" s="44"/>
-      <c r="J86" s="45"/>
-    </row>
-    <row r="87" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I86" s="36"/>
+      <c r="J86" s="37"/>
+    </row>
+    <row r="87" spans="1:10" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="9"/>
-      <c r="B87" s="28" t="s">
+      <c r="B87" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="C87" s="72"/>
+      <c r="D87" s="73"/>
+      <c r="E87" s="20">
+        <v>5</v>
+      </c>
+      <c r="F87" s="21"/>
+      <c r="G87" s="22"/>
+      <c r="H87" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>راسب</v>
+      </c>
+      <c r="I87" s="32"/>
+      <c r="J87" s="33"/>
+    </row>
+    <row r="88" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="9"/>
+      <c r="B88" s="71" t="s">
         <v>107</v>
       </c>
-      <c r="C87" s="29"/>
-      <c r="D87" s="30"/>
-      <c r="E87" s="20">
-        <v>5</v>
-      </c>
-      <c r="F87" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G87" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="H87" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I87" s="40"/>
-      <c r="J87" s="41"/>
-    </row>
-    <row r="88" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="9"/>
-      <c r="B88" s="28" t="s">
+      <c r="C88" s="72"/>
+      <c r="D88" s="73"/>
+      <c r="E88" s="20">
+        <v>5</v>
+      </c>
+      <c r="F88" s="21"/>
+      <c r="G88" s="22"/>
+      <c r="H88" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>راسب</v>
+      </c>
+      <c r="I88" s="32"/>
+      <c r="J88" s="33"/>
+    </row>
+    <row r="89" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="9"/>
+      <c r="B89" s="71" t="s">
         <v>108</v>
       </c>
-      <c r="C88" s="29"/>
-      <c r="D88" s="30"/>
-      <c r="E88" s="20">
-        <v>5</v>
-      </c>
-      <c r="F88" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G88" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="H88" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I88" s="40"/>
-      <c r="J88" s="41"/>
-    </row>
-    <row r="89" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="9"/>
-      <c r="B89" s="28" t="s">
+      <c r="C89" s="72"/>
+      <c r="D89" s="73"/>
+      <c r="E89" s="20">
+        <v>5</v>
+      </c>
+      <c r="F89" s="21"/>
+      <c r="G89" s="22"/>
+      <c r="H89" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>راسب</v>
+      </c>
+      <c r="I89" s="32"/>
+      <c r="J89" s="33"/>
+    </row>
+    <row r="90" spans="1:10" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="9"/>
+      <c r="B90" s="74" t="s">
         <v>109</v>
       </c>
-      <c r="C89" s="29"/>
-      <c r="D89" s="30"/>
-      <c r="E89" s="20">
-        <v>5</v>
-      </c>
-      <c r="F89" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G89" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="H89" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I89" s="40"/>
-      <c r="J89" s="41"/>
-    </row>
-    <row r="90" spans="1:10" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="9"/>
-      <c r="B90" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="C90" s="32"/>
-      <c r="D90" s="33"/>
+      <c r="C90" s="75"/>
+      <c r="D90" s="76"/>
       <c r="E90" s="24">
         <v>6</v>
       </c>
-      <c r="F90" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="G90" s="26" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="F90" s="25"/>
+      <c r="G90" s="26"/>
       <c r="H90" s="27" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I90" s="51"/>
-      <c r="J90" s="52"/>
-    </row>
-    <row r="91" spans="1:10" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>راسب</v>
+      </c>
+      <c r="I90" s="34"/>
+      <c r="J90" s="35"/>
+    </row>
+    <row r="91" spans="1:10" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="9"/>
-      <c r="B91" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="C91" s="35"/>
-      <c r="D91" s="36"/>
+      <c r="B91" s="65" t="s">
+        <v>110</v>
+      </c>
+      <c r="C91" s="66"/>
+      <c r="D91" s="67"/>
       <c r="E91" s="8">
         <v>8</v>
       </c>
-      <c r="F91" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G91" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="F91" s="14"/>
+      <c r="G91" s="15"/>
       <c r="H91" s="13" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I91" s="42"/>
-      <c r="J91" s="43"/>
-    </row>
-    <row r="92" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>راسب</v>
+      </c>
+      <c r="I91" s="28"/>
+      <c r="J91" s="29"/>
+    </row>
+    <row r="92" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="9"/>
-      <c r="B92" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="C92" s="35"/>
-      <c r="D92" s="36"/>
+      <c r="B92" s="65" t="s">
+        <v>111</v>
+      </c>
+      <c r="C92" s="66"/>
+      <c r="D92" s="67"/>
       <c r="E92" s="8">
         <v>8</v>
       </c>
-      <c r="F92" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G92" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="F92" s="14"/>
+      <c r="G92" s="15"/>
       <c r="H92" s="13" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I92" s="42"/>
-      <c r="J92" s="43"/>
-    </row>
-    <row r="93" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>راسب</v>
+      </c>
+      <c r="I92" s="28"/>
+      <c r="J92" s="29"/>
+    </row>
+    <row r="93" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="3"/>
-      <c r="B93" s="76" t="s">
-        <v>5</v>
-      </c>
-      <c r="C93" s="68"/>
-      <c r="D93" s="68"/>
+      <c r="B93" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="C93" s="31"/>
+      <c r="D93" s="31"/>
       <c r="E93" s="8">
         <f>SUM(E8:E92)</f>
         <v>470</v>
@@ -4172,79 +3775,246 @@
         <f>SUM(F8:F92)</f>
         <v>0</v>
       </c>
-      <c r="G93" s="48"/>
-      <c r="H93" s="49"/>
-      <c r="I93" s="49"/>
-      <c r="J93" s="50"/>
-    </row>
-    <row r="94" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G93" s="62"/>
+      <c r="H93" s="63"/>
+      <c r="I93" s="63"/>
+      <c r="J93" s="64"/>
+    </row>
+    <row r="94" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="3"/>
-      <c r="B94" s="76" t="s">
+      <c r="B94" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="C94" s="68"/>
-      <c r="D94" s="68"/>
-      <c r="E94" s="60">
+      <c r="C94" s="31"/>
+      <c r="D94" s="31"/>
+      <c r="E94" s="51">
         <f>F93/E93/100*100</f>
         <v>0</v>
       </c>
-      <c r="F94" s="60"/>
-      <c r="G94" s="60"/>
-      <c r="H94" s="60"/>
-      <c r="I94" s="60"/>
-      <c r="J94" s="61"/>
-    </row>
-    <row r="95" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F94" s="51"/>
+      <c r="G94" s="51"/>
+      <c r="H94" s="51"/>
+      <c r="I94" s="51"/>
+      <c r="J94" s="52"/>
+    </row>
+    <row r="95" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="3"/>
-      <c r="B95" s="76" t="s">
+      <c r="B95" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C95" s="68"/>
-      <c r="D95" s="68"/>
-      <c r="E95" s="74" t="str">
+      <c r="C95" s="31"/>
+      <c r="D95" s="31"/>
+      <c r="E95" s="42" t="str">
         <f>_xlfn.IFS(E94&gt;=90%,"ممتاز",E94&gt;=80%,"جيد جداً",E94&gt;=70%,"جيد",E94&gt;=60%,"مقبول",E94&lt;60%,"راسب")</f>
         <v>راسب</v>
       </c>
-      <c r="F95" s="74"/>
-      <c r="G95" s="74"/>
-      <c r="H95" s="74"/>
-      <c r="I95" s="74"/>
-      <c r="J95" s="75"/>
-    </row>
-    <row r="96" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B96" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="C96" s="70"/>
-      <c r="D96" s="70"/>
-      <c r="E96" s="46" t="s">
+      <c r="F95" s="42"/>
+      <c r="G95" s="42"/>
+      <c r="H95" s="42"/>
+      <c r="I95" s="42"/>
+      <c r="J95" s="43"/>
+    </row>
+    <row r="96" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B96" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C96" s="38"/>
+      <c r="D96" s="38"/>
+      <c r="E96" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="F96" s="46"/>
-      <c r="G96" s="72" t="s">
+      <c r="F96" s="60"/>
+      <c r="G96" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="H96" s="72"/>
-      <c r="I96" s="72"/>
-      <c r="J96" s="72"/>
-    </row>
-    <row r="97" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H96" s="40"/>
+      <c r="I96" s="40"/>
+      <c r="J96" s="40"/>
+    </row>
+    <row r="97" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4"/>
-      <c r="B97" s="71"/>
-      <c r="C97" s="71"/>
-      <c r="D97" s="71"/>
-      <c r="E97" s="47" t="s">
+      <c r="B97" s="39"/>
+      <c r="C97" s="39"/>
+      <c r="D97" s="39"/>
+      <c r="E97" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="F97" s="47"/>
-      <c r="G97" s="73"/>
-      <c r="H97" s="73"/>
-      <c r="I97" s="73"/>
-      <c r="J97" s="73"/>
+      <c r="F97" s="61"/>
+      <c r="G97" s="41"/>
+      <c r="H97" s="41"/>
+      <c r="I97" s="41"/>
+      <c r="J97" s="41"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="191">
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B91:D91"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B81:D81"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="E96:F96"/>
+    <mergeCell ref="E97:F97"/>
+    <mergeCell ref="G93:J93"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="I67:J67"/>
+    <mergeCell ref="I68:J68"/>
+    <mergeCell ref="I69:J69"/>
+    <mergeCell ref="I70:J70"/>
+    <mergeCell ref="I71:J71"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="I73:J73"/>
+    <mergeCell ref="I74:J74"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="I76:J76"/>
+    <mergeCell ref="I77:J77"/>
+    <mergeCell ref="I78:J78"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="B5:D6"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="E94:J94"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I84:J84"/>
+    <mergeCell ref="I85:J85"/>
+    <mergeCell ref="I86:J86"/>
+    <mergeCell ref="I87:J87"/>
+    <mergeCell ref="I88:J88"/>
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="I91:J91"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I5:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="B96:D97"/>
+    <mergeCell ref="G96:J96"/>
+    <mergeCell ref="G97:J97"/>
+    <mergeCell ref="E95:J95"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="I80:J80"/>
+    <mergeCell ref="I81:J81"/>
+    <mergeCell ref="I82:J82"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="I55:J55"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="I92:J92"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="B93:D93"/>
     <mergeCell ref="B94:D94"/>
@@ -4269,173 +4039,6 @@
     <mergeCell ref="I20:J20"/>
     <mergeCell ref="I21:J21"/>
     <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B96:D97"/>
-    <mergeCell ref="G96:J96"/>
-    <mergeCell ref="G97:J97"/>
-    <mergeCell ref="E95:J95"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I80:J80"/>
-    <mergeCell ref="I81:J81"/>
-    <mergeCell ref="I82:J82"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="I54:J54"/>
-    <mergeCell ref="I55:J55"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="I58:J58"/>
-    <mergeCell ref="I92:J92"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="B5:D6"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="E94:J94"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I84:J84"/>
-    <mergeCell ref="I85:J85"/>
-    <mergeCell ref="I86:J86"/>
-    <mergeCell ref="I87:J87"/>
-    <mergeCell ref="I88:J88"/>
-    <mergeCell ref="I90:J90"/>
-    <mergeCell ref="I91:J91"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I5:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="E96:F96"/>
-    <mergeCell ref="E97:F97"/>
-    <mergeCell ref="G93:J93"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="I62:J62"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="I66:J66"/>
-    <mergeCell ref="I67:J67"/>
-    <mergeCell ref="I68:J68"/>
-    <mergeCell ref="I69:J69"/>
-    <mergeCell ref="I70:J70"/>
-    <mergeCell ref="I71:J71"/>
-    <mergeCell ref="I72:J72"/>
-    <mergeCell ref="I73:J73"/>
-    <mergeCell ref="I74:J74"/>
-    <mergeCell ref="I75:J75"/>
-    <mergeCell ref="I76:J76"/>
-    <mergeCell ref="I77:J77"/>
-    <mergeCell ref="I78:J78"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B91:D91"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B81:D81"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="B88:D88"/>
   </mergeCells>
   <conditionalFormatting sqref="E95">
     <cfRule type="expression" dxfId="23" priority="57">
@@ -4535,9 +4138,17 @@
       <formula>NOT(ISERROR(SEARCH("أدخل العلامة",F9)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:J2" xr:uid="{F27846E5-4775-4613-AD3F-6A647663FDD7}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8 F34:F46 F48:F53 F55:F58 C2:D3 G96:J96 F3:J3 F75:F85 F60:F73 F87:F92 F23:F32 F10:F21" xr:uid="{29F5EBBB-8CF0-4EBC-9568-49582573F3A1}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="75" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="74" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"-,Bold"&amp;12&amp;Uسري للغاية</oddHeader>
     <oddFooter>&amp;C&amp;"-,Bold"&amp;P&amp;"-,Regular"
@@ -4546,59 +4157,5 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="32" max="9" man="1"/>
   </rowBreaks>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F27846E5-4775-4613-AD3F-6A647663FDD7}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2:J2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{29F5EBBB-8CF0-4EBC-9568-49582573F3A1}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>C2:D2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5A7ADC9F-6098-4415-8DD4-849A148D02E3}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>F15:F17 F75:F85 F60:F73 F32 F87:F89 F23:F29 F21 F13 F10</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BD8CB5A2-5F32-4EAD-A63C-382D3B90B847}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>G96:J96 F3:J3</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{132078BB-599D-4F0E-87F8-5A950BE5625D}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>C3:D3</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8D4D43B9-DD7F-460A-8835-21D9C8972F3E}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>F8 F12 F14 F46 F48 F49 F55</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7ECEABBE-C49A-47D7-824F-0D321C7BFC23}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>F11 F19 F50 F51 F52 F53 F56 F57 F58 F91 F92</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5C087469-F938-446E-BF86-01C65D256790}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>F90 F45 F44 F43 F42 F41 F40 F39 F38 F37 F36 F35 F34 F31 F30 F20 F18</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>